--- a/data/trans_bre/IP15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,84; 11,74</t>
+          <t>-6,66; 11,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,75; 6,3</t>
+          <t>-10,92; 6,32</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,81; 8,72</t>
+          <t>-6,58; 9,08</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-21,23; 3,42</t>
+          <t>-22,52; 3,7</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-23,68; 56,78</t>
+          <t>-24,05; 57,64</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,24; 28,82</t>
+          <t>-34,32; 28,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,93; 57,68</t>
+          <t>-29,17; 59,8</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-49,64; 14,37</t>
+          <t>-51,97; 13,11</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,16; 2,5</t>
+          <t>-8,85; 2,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,19; 4,63</t>
+          <t>-8,53; 3,73</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,65; 8,95</t>
+          <t>-2,81; 8,7</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 11,01</t>
+          <t>-5,64; 10,22</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-37,17; 13,97</t>
+          <t>-38,42; 16,08</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,15; 21,33</t>
+          <t>-30,75; 17,58</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-13,15; 62,8</t>
+          <t>-15,89; 61,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-20,96; 47,77</t>
+          <t>-19,55; 43,25</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,28; 8,32</t>
+          <t>-6,79; 7,81</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,75; 7,86</t>
+          <t>-5,29; 9,42</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,81; 7,81</t>
+          <t>-5,3; 8,02</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,04; 7,9</t>
+          <t>-7,57; 8,04</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-30,5; 62,59</t>
+          <t>-34,81; 62,1</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-27,01; 58,66</t>
+          <t>-26,02; 70,13</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-27,32; 54,19</t>
+          <t>-24,92; 56,66</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-28,51; 41,8</t>
+          <t>-29,08; 43,77</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,67; 2,68</t>
+          <t>-9,26; 3,2</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,26; 8,26</t>
+          <t>-4,19; 8,62</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,74; 6,13</t>
+          <t>-6,54; 5,84</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,12; 30,81</t>
+          <t>-3,69; 28,84</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,75; 18,87</t>
+          <t>-42,14; 21,23</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-24,83; 78,38</t>
+          <t>-25,05; 81,53</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,15; 60,68</t>
+          <t>-41,28; 58,57</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,75; 168,18</t>
+          <t>-15,86; 167,61</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-5,16; 1,55</t>
+          <t>-4,73; 1,72</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,67; 3,41</t>
+          <t>-3,8; 3,59</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,48; 4,82</t>
+          <t>-1,8; 5,2</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,09; 13,14</t>
+          <t>-2,23; 12,9</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-23,38; 8,31</t>
+          <t>-21,96; 9,04</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,33; 17,62</t>
+          <t>-16,67; 18,49</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-8,09; 32,24</t>
+          <t>-10,0; 35,2</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,77; 55,73</t>
+          <t>-8,96; 58,18</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Edad-trans_bre.xlsx
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-6,66; 11,61</t>
+          <t>-5,86; 13,22</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,92; 6,32</t>
+          <t>-10,56; 6,5</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,58; 9,08</t>
+          <t>-6,59; 9,12</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-22,52; 3,7</t>
+          <t>-20,76; 4,35</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-24,05; 57,64</t>
+          <t>-20,59; 68,41</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,32; 28,71</t>
+          <t>-34,9; 29,48</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,17; 59,8</t>
+          <t>-29,26; 57,22</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-51,97; 13,11</t>
+          <t>-48,8; 18,66</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,85; 2,72</t>
+          <t>-8,36; 2,25</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-8,53; 3,73</t>
+          <t>-9,21; 3,87</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 8,7</t>
+          <t>-2,69; 9,13</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-5,64; 10,22</t>
+          <t>-6,05; 11,33</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-38,42; 16,08</t>
+          <t>-36,11; 13,23</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-30,75; 17,58</t>
+          <t>-31,12; 17,88</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 61,33</t>
+          <t>-14,16; 67,33</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,55; 43,25</t>
+          <t>-19,22; 52,36</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,79; 7,81</t>
+          <t>-6,22; 8,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,29; 9,42</t>
+          <t>-5,77; 8,62</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-5,3; 8,02</t>
+          <t>-4,52; 8,98</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-7,57; 8,04</t>
+          <t>-6,83; 7,62</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-34,81; 62,1</t>
+          <t>-31,58; 64,29</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-26,02; 70,13</t>
+          <t>-28,54; 59,58</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-24,92; 56,66</t>
+          <t>-21,93; 61,34</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-29,08; 43,77</t>
+          <t>-27,59; 43,97</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-9,26; 3,2</t>
+          <t>-8,96; 2,92</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,19; 8,62</t>
+          <t>-4,04; 8,12</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,54; 5,84</t>
+          <t>-6,41; 5,53</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,69; 28,84</t>
+          <t>-3,08; 26,94</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-42,14; 21,23</t>
+          <t>-41,49; 18,06</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-25,05; 81,53</t>
+          <t>-23,94; 75,15</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-41,28; 58,57</t>
+          <t>-40,52; 54,3</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-15,86; 167,61</t>
+          <t>-16,27; 166,66</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,73; 1,72</t>
+          <t>-4,82; 1,75</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,8; 3,59</t>
+          <t>-3,73; 3,14</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-1,8; 5,2</t>
+          <t>-2,02; 4,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,23; 12,9</t>
+          <t>-2,81; 12,94</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-21,96; 9,04</t>
+          <t>-22,21; 9,43</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,67; 18,49</t>
+          <t>-16,39; 15,78</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,0; 35,2</t>
+          <t>-10,74; 29,52</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 58,18</t>
+          <t>-10,98; 57,91</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Edad-trans_bre.xlsx
@@ -522,7 +522,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que consumiero medicamentos (gotas/pastillas, inyecciones, supositorios,etc..)</t>
+          <t>Menores que consumieron algún tipo de medicamento en las últimas 2 semanas</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -627,7 +627,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>-8,59</t>
+          <t>-7,29</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -647,7 +647,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>-23,62%</t>
+          <t>-21,14%</t>
         </is>
       </c>
     </row>
@@ -660,42 +660,42 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>-5,86; 13,22</t>
+          <t>-6,84; 11,74</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>-10,56; 6,5</t>
+          <t>-10,75; 6,3</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-6,59; 9,12</t>
+          <t>-6,81; 8,72</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-20,76; 4,35</t>
+          <t>-19,25; 4,5</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-20,59; 68,41</t>
+          <t>-23,68; 56,78</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-34,9; 29,48</t>
+          <t>-34,24; 28,82</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>-29,26; 57,22</t>
+          <t>-29,93; 57,68</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>-48,8; 18,66</t>
+          <t>-48,43; 17,44</t>
         </is>
       </c>
     </row>
@@ -727,7 +727,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2,33</t>
+          <t>1,82</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -747,7 +747,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>8,65%</t>
+          <t>6,94%</t>
         </is>
       </c>
     </row>
@@ -760,42 +760,42 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>-8,36; 2,25</t>
+          <t>-8,16; 2,5</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>-9,21; 3,87</t>
+          <t>-8,19; 4,63</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 9,13</t>
+          <t>-2,65; 8,95</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>-6,05; 11,33</t>
+          <t>-6,93; 10,01</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>-36,11; 13,23</t>
+          <t>-37,17; 13,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>-31,12; 17,88</t>
+          <t>-30,15; 21,33</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>-14,16; 67,33</t>
+          <t>-13,15; 62,8</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>-19,22; 52,36</t>
+          <t>-23,56; 42,17</t>
         </is>
       </c>
     </row>
@@ -827,7 +827,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>0,18</t>
+          <t>-0,14</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -847,7 +847,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>0,83%</t>
+          <t>-0,63%</t>
         </is>
       </c>
     </row>
@@ -860,42 +860,42 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-6,22; 8,43</t>
+          <t>-6,28; 8,32</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-5,77; 8,62</t>
+          <t>-5,75; 7,86</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>-4,52; 8,98</t>
+          <t>-5,81; 7,81</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>-6,83; 7,62</t>
+          <t>-7,59; 7,44</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>-31,58; 64,29</t>
+          <t>-30,5; 62,59</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>-28,54; 59,58</t>
+          <t>-27,01; 58,66</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>-21,93; 61,34</t>
+          <t>-27,32; 54,19</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>-27,59; 43,97</t>
+          <t>-29,32; 38,84</t>
         </is>
       </c>
     </row>
@@ -927,7 +927,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>7,12</t>
+          <t>-1,81</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -947,7 +947,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>33,64%</t>
+          <t>-8,51%</t>
         </is>
       </c>
     </row>
@@ -960,42 +960,42 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>-8,96; 2,92</t>
+          <t>-9,67; 2,68</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 8,12</t>
+          <t>-4,26; 8,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>-6,41; 5,53</t>
+          <t>-6,74; 6,13</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>-3,08; 26,94</t>
+          <t>-8,86; 4,65</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>-41,49; 18,06</t>
+          <t>-41,75; 18,87</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-23,94; 75,15</t>
+          <t>-24,83; 78,38</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>-40,52; 54,3</t>
+          <t>-41,15; 60,68</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>-16,27; 166,66</t>
+          <t>-34,58; 25,05</t>
         </is>
       </c>
     </row>
@@ -1027,7 +1027,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>2,92</t>
+          <t>-0,79</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1047,7 +1047,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>12,19%</t>
+          <t>-3,34%</t>
         </is>
       </c>
     </row>
@@ -1060,42 +1060,42 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>-4,82; 1,75</t>
+          <t>-5,16; 1,55</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>-3,73; 3,14</t>
+          <t>-3,67; 3,41</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-2,02; 4,51</t>
+          <t>-1,48; 4,82</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-2,81; 12,94</t>
+          <t>-5,06; 3,21</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-22,21; 9,43</t>
+          <t>-23,38; 8,31</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-16,39; 15,78</t>
+          <t>-16,33; 17,62</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>-10,74; 29,52</t>
+          <t>-8,09; 32,24</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>-10,98; 57,91</t>
+          <t>-19,07; 15,08</t>
         </is>
       </c>
     </row>

--- a/data/trans_bre/IP15-Edad-trans_bre.xlsx
+++ b/data/trans_bre/IP15-Edad-trans_bre.xlsx
@@ -16,7 +16,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
+  <numFmts count="2">
+    <numFmt numFmtId="164" formatCode="0.##"/>
+    <numFmt numFmtId="165" formatCode="0.##%"/>
+  </numFmts>
   <fonts count="2">
     <font>
       <name val="Calibri"/>
@@ -125,7 +128,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -138,6 +141,12 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="bottom"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -504,7 +513,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J14"/>
+  <dimension ref="A1:J19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -610,299 +619,199 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>2,92</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>-1,45</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>1,22</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>-7,29</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>11,93%</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>-5,52%</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>6,34%</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>-21,14%</t>
-        </is>
+      <c r="C4" s="5" t="n">
+        <v>2.915734031797529</v>
+      </c>
+      <c r="D4" s="5" t="n">
+        <v>-1.452163893089145</v>
+      </c>
+      <c r="E4" s="5" t="n">
+        <v>1.223550771090895</v>
+      </c>
+      <c r="F4" s="5" t="n">
+        <v>-7.293673238666765</v>
+      </c>
+      <c r="G4" s="6" t="n">
+        <v>0.1193433943715298</v>
+      </c>
+      <c r="H4" s="6" t="n">
+        <v>-0.05517164234437947</v>
+      </c>
+      <c r="I4" s="6" t="n">
+        <v>0.06336394519670227</v>
+      </c>
+      <c r="J4" s="6" t="n">
+        <v>-0.2114448861891528</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>-6,84; 11,74</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>-10,75; 6,3</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>-6,81; 8,72</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>-19,25; 4,5</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>-23,68; 56,78</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>-34,24; 28,82</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>-29,93; 57,68</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>-48,43; 17,44</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C5" s="5" t="n">
+        <v>-6.842595935347298</v>
+      </c>
+      <c r="D5" s="5" t="n">
+        <v>-10.74633912135373</v>
+      </c>
+      <c r="E5" s="5" t="n">
+        <v>-6.80963685484568</v>
+      </c>
+      <c r="F5" s="5" t="n">
+        <v>-19.24803241549083</v>
+      </c>
+      <c r="G5" s="6" t="n">
+        <v>-0.2368169331569858</v>
+      </c>
+      <c r="H5" s="6" t="n">
+        <v>-0.3424499657238016</v>
+      </c>
+      <c r="I5" s="6" t="n">
+        <v>-0.2993198261231618</v>
+      </c>
+      <c r="J5" s="6" t="n">
+        <v>-0.484336274721988</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="1" t="inlineStr">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C6" s="5" t="n">
+        <v>11.74103281357362</v>
+      </c>
+      <c r="D6" s="5" t="n">
+        <v>6.299039039738317</v>
+      </c>
+      <c r="E6" s="5" t="n">
+        <v>8.722139701905055</v>
+      </c>
+      <c r="F6" s="5" t="n">
+        <v>4.49938745706643</v>
+      </c>
+      <c r="G6" s="6" t="n">
+        <v>0.5678224755194015</v>
+      </c>
+      <c r="H6" s="6" t="n">
+        <v>0.2881859751710854</v>
+      </c>
+      <c r="I6" s="6" t="n">
+        <v>0.5768120861643871</v>
+      </c>
+      <c r="J6" s="6" t="n">
+        <v>0.1744261244882802</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
         <is>
           <t>3-7</t>
         </is>
       </c>
-      <c r="B6" s="3" t="inlineStr">
+      <c r="B7" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>-3,01</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>-2,12</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>3,36</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>1,82</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>-15,0%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>-8,45%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>20,15%</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>6,94%</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="1" t="n"/>
-      <c r="B7" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>-8,16; 2,5</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>-8,19; 4,63</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>-2,65; 8,95</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>-6,93; 10,01</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>-37,17; 13,97</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>-30,15; 21,33</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>-13,15; 62,8</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>-23,56; 42,17</t>
-        </is>
+      <c r="C7" s="5" t="n">
+        <v>-3.012807238972945</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>-2.116676285939548</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>3.364505338361207</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>1.823553032984815</v>
+      </c>
+      <c r="G7" s="6" t="n">
+        <v>-0.1500233384936757</v>
+      </c>
+      <c r="H7" s="6" t="n">
+        <v>-0.08452007566764994</v>
+      </c>
+      <c r="I7" s="6" t="n">
+        <v>0.2014681140439457</v>
+      </c>
+      <c r="J7" s="6" t="n">
+        <v>0.06938895141695609</v>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="1" t="inlineStr">
-        <is>
-          <t>8-11</t>
-        </is>
-      </c>
+      <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Estimación</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>0,78</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>1,33</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>1,39</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>-0,14</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4,63%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>7,51%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>7,82%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>-0,63%</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>-8.159368456967918</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>-8.187564556627226</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>-2.649403386513967</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>-6.932425278482246</v>
+      </c>
+      <c r="G8" s="6" t="n">
+        <v>-0.3716643536259671</v>
+      </c>
+      <c r="H8" s="6" t="n">
+        <v>-0.3015254982520795</v>
+      </c>
+      <c r="I8" s="6" t="n">
+        <v>-0.131490583331893</v>
+      </c>
+      <c r="J8" s="6" t="n">
+        <v>-0.2356372341066012</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="n"/>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>-6,28; 8,32</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>-5,75; 7,86</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>-5,81; 7,81</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>-7,59; 7,44</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>-30,5; 62,59</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>-27,01; 58,66</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>-27,32; 54,19</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>-29,32; 38,84</t>
-        </is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C9" s="5" t="n">
+        <v>2.496116667600091</v>
+      </c>
+      <c r="D9" s="5" t="n">
+        <v>4.629628096333698</v>
+      </c>
+      <c r="E9" s="5" t="n">
+        <v>8.954223848031768</v>
+      </c>
+      <c r="F9" s="5" t="n">
+        <v>10.01239067358071</v>
+      </c>
+      <c r="G9" s="6" t="n">
+        <v>0.1397361366182242</v>
+      </c>
+      <c r="H9" s="6" t="n">
+        <v>0.2132611955454691</v>
+      </c>
+      <c r="I9" s="6" t="n">
+        <v>0.6280122326325338</v>
+      </c>
+      <c r="J9" s="6" t="n">
+        <v>0.4217138229957559</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
-          <t>12-15</t>
+          <t>8-11</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -910,197 +819,297 @@
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
-        <is>
-          <t>-3,4</t>
-        </is>
-      </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>1,98</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>-0,34</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>-1,81</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>-17,78%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,29%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>-2,63%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>-8,51%</t>
-        </is>
+      <c r="C10" s="5" t="n">
+        <v>0.7807700105622595</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>1.329097407652763</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>1.386596250804048</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>-0.1383088941682403</v>
+      </c>
+      <c r="G10" s="6" t="n">
+        <v>0.04629580739918413</v>
+      </c>
+      <c r="H10" s="6" t="n">
+        <v>0.07512857575234762</v>
+      </c>
+      <c r="I10" s="6" t="n">
+        <v>0.07817676990661089</v>
+      </c>
+      <c r="J10" s="6" t="n">
+        <v>-0.006294829100268177</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="inlineStr">
-        <is>
-          <t>-9,67; 2,68</t>
-        </is>
-      </c>
-      <c r="D11" s="2" t="inlineStr">
-        <is>
-          <t>-4,26; 8,26</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>-6,74; 6,13</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>-8,86; 4,65</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>-41,75; 18,87</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>-24,83; 78,38</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="inlineStr">
-        <is>
-          <t>-41,15; 60,68</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>-34,58; 25,05</t>
-        </is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>-6.282960721185969</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-5.753079035375449</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>-5.807508370709195</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>-7.593862599702629</v>
+      </c>
+      <c r="G11" s="6" t="n">
+        <v>-0.3049888716198129</v>
+      </c>
+      <c r="H11" s="6" t="n">
+        <v>-0.270091312984631</v>
+      </c>
+      <c r="I11" s="6" t="n">
+        <v>-0.2732442387201842</v>
+      </c>
+      <c r="J11" s="6" t="n">
+        <v>-0.293208802746524</v>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="1" t="inlineStr">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C12" s="5" t="n">
+        <v>8.315164983775549</v>
+      </c>
+      <c r="D12" s="5" t="n">
+        <v>7.855204066509827</v>
+      </c>
+      <c r="E12" s="5" t="n">
+        <v>7.805983084645125</v>
+      </c>
+      <c r="F12" s="5" t="n">
+        <v>7.435953430070078</v>
+      </c>
+      <c r="G12" s="6" t="n">
+        <v>0.6258983220025509</v>
+      </c>
+      <c r="H12" s="6" t="n">
+        <v>0.5866467365176092</v>
+      </c>
+      <c r="I12" s="6" t="n">
+        <v>0.5419034678080122</v>
+      </c>
+      <c r="J12" s="6" t="n">
+        <v>0.3884148784927632</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>Estimación</t>
+        </is>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>-3.403981728544886</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1.98222978771315</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>-0.3433346467865833</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>-1.8118003833895</v>
+      </c>
+      <c r="G13" s="6" t="n">
+        <v>-0.1778460488309129</v>
+      </c>
+      <c r="H13" s="6" t="n">
+        <v>0.1428660036512843</v>
+      </c>
+      <c r="I13" s="6" t="n">
+        <v>-0.02625775223480404</v>
+      </c>
+      <c r="J13" s="6" t="n">
+        <v>-0.08508864989866051</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-9.665142585730299</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-4.255928085178516</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-6.735603249782997</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-8.855512825518701</v>
+      </c>
+      <c r="G14" s="6" t="n">
+        <v>-0.4174723173023458</v>
+      </c>
+      <c r="H14" s="6" t="n">
+        <v>-0.2483071323210974</v>
+      </c>
+      <c r="I14" s="6" t="n">
+        <v>-0.4115001143939549</v>
+      </c>
+      <c r="J14" s="6" t="n">
+        <v>-0.3457738851573913</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>2.684073448057579</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>8.262745904869234</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>6.132554598869013</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4.646815129736198</v>
+      </c>
+      <c r="G15" s="6" t="n">
+        <v>0.1887135357268869</v>
+      </c>
+      <c r="H15" s="6" t="n">
+        <v>0.7838262941105683</v>
+      </c>
+      <c r="I15" s="6" t="n">
+        <v>0.6067572503801986</v>
+      </c>
+      <c r="J15" s="6" t="n">
+        <v>0.2504842637356343</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
-      <c r="B12" s="3" t="inlineStr">
+      <c r="B16" s="3" t="inlineStr">
         <is>
           <t>Estimación</t>
         </is>
       </c>
-      <c r="C12" s="2" t="inlineStr">
-        <is>
-          <t>-1,51</t>
-        </is>
-      </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>-0,32</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>1,55</t>
-        </is>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>-0,79</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>-7,6%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>-1,54%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>9,34%</t>
-        </is>
-      </c>
-      <c r="J12" s="2" t="inlineStr">
-        <is>
-          <t>-3,34%</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="1" t="n"/>
-      <c r="B13" s="3" t="inlineStr">
-        <is>
-          <t>IC 95%</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>-5,16; 1,55</t>
-        </is>
-      </c>
-      <c r="D13" s="2" t="inlineStr">
-        <is>
-          <t>-3,67; 3,41</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>-1,48; 4,82</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>-5,06; 3,21</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>-23,38; 8,31</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>-16,33; 17,62</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>-8,09; 32,24</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>-19,07; 15,08</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
+      <c r="C16" s="5" t="n">
+        <v>-1.514437309679839</v>
+      </c>
+      <c r="D16" s="5" t="n">
+        <v>-0.3245011576576418</v>
+      </c>
+      <c r="E16" s="5" t="n">
+        <v>1.54513693779936</v>
+      </c>
+      <c r="F16" s="5" t="n">
+        <v>-0.7866723337066284</v>
+      </c>
+      <c r="G16" s="6" t="n">
+        <v>-0.07604862347984856</v>
+      </c>
+      <c r="H16" s="6" t="n">
+        <v>-0.01538887975729601</v>
+      </c>
+      <c r="I16" s="6" t="n">
+        <v>0.09335851419593136</v>
+      </c>
+      <c r="J16" s="6" t="n">
+        <v>-0.03339386391292328</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% inferior</t>
+        </is>
+      </c>
+      <c r="C17" s="5" t="n">
+        <v>-5.162714120891358</v>
+      </c>
+      <c r="D17" s="5" t="n">
+        <v>-3.672013901096685</v>
+      </c>
+      <c r="E17" s="5" t="n">
+        <v>-1.476697057000417</v>
+      </c>
+      <c r="F17" s="5" t="n">
+        <v>-5.057411194845664</v>
+      </c>
+      <c r="G17" s="6" t="n">
+        <v>-0.2338327333113071</v>
+      </c>
+      <c r="H17" s="6" t="n">
+        <v>-0.1633162595385603</v>
+      </c>
+      <c r="I17" s="6" t="n">
+        <v>-0.08089991387708446</v>
+      </c>
+      <c r="J17" s="6" t="n">
+        <v>-0.1907488236076569</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95% superior</t>
+        </is>
+      </c>
+      <c r="C18" s="5" t="n">
+        <v>1.551920647295891</v>
+      </c>
+      <c r="D18" s="5" t="n">
+        <v>3.408520049708221</v>
+      </c>
+      <c r="E18" s="5" t="n">
+        <v>4.817980716713777</v>
+      </c>
+      <c r="F18" s="5" t="n">
+        <v>3.206052157279022</v>
+      </c>
+      <c r="G18" s="6" t="n">
+        <v>0.08308181202454276</v>
+      </c>
+      <c r="H18" s="6" t="n">
+        <v>0.1762052422905753</v>
+      </c>
+      <c r="I18" s="6" t="n">
+        <v>0.3224405682661183</v>
+      </c>
+      <c r="J18" s="6" t="n">
+        <v>0.1507688055081483</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
         <is>
           <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
         </is>
@@ -1108,14 +1117,14 @@
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="A12:A13"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
     <mergeCell ref="C1:F1"/>
     <mergeCell ref="G1:J1"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="A10:A11"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="A13:A15"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
